--- a/artfynd/A 37626-2024 artfynd.xlsx
+++ b/artfynd/A 37626-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -911,6 +911,1264 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>123352848</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57631</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Ramsebo Gölkullen, Hultsfred, Ramsebo Gölkullen, Hultsfred, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>539517</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6348531</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Hultsfred</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Virserum</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>123352763</v>
+      </c>
+      <c r="B5" t="n">
+        <v>98365</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Ramsebo Gölkullen, Hultsfred, Ramsebo Gölkullen, Hultsfred, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>539512</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6348548</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Hultsfred</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Virserum</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>123354802</v>
+      </c>
+      <c r="B6" t="n">
+        <v>100631</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Ramsebo Gölkullen, Hultsfred, Ramsebo Gölkullen, Hultsfred, Sm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>539539</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6348519</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Hultsfred</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Virserum</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>123354688</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57631</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Ramsebo Gölkullen, Hultsfred, Ramsebo Gölkullen, Hultsfred, Sm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>539536</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6348529</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Hultsfred</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Virserum</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>123352575</v>
+      </c>
+      <c r="B8" t="n">
+        <v>92233</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Ramsebo Gölkullen, Hultsfred, Ramsebo Gölkullen, Hultsfred, Sm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>539489</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6348577</v>
+      </c>
+      <c r="S8" t="n">
+        <v>15</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Hultsfred</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Virserum</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>123353224</v>
+      </c>
+      <c r="B9" t="n">
+        <v>98365</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Ramsebo Gölkullen, Hultsfred, Ramsebo Gölkullen, Hultsfred, Sm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>539470</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6348541</v>
+      </c>
+      <c r="S9" t="n">
+        <v>15</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Hultsfred</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Virserum</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>123353834</v>
+      </c>
+      <c r="B10" t="n">
+        <v>92233</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Ramsebo Gölkullen, Hultsfred, Ramsebo Gölkullen, Hultsfred, Sm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>539458</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6348572</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Hultsfred</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Virserum</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>God förekomst, spridd i slänten</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>123353749</v>
+      </c>
+      <c r="B11" t="n">
+        <v>92233</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Ramsebo Gölkullen, Hultsfred, Ramsebo Gölkullen, Hultsfred, Sm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>539463</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6348578</v>
+      </c>
+      <c r="S11" t="n">
+        <v>15</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Hultsfred</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Virserum</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>123352400</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57494</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Ramsebo Gölkullen, Hultsfred, Ramsebo Gölkullen, Hultsfred, Sm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>539450</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6348650</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Hultsfred</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Virserum</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>123354501</v>
+      </c>
+      <c r="B13" t="n">
+        <v>105432</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>340</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Ryl</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Chimaphila umbellata</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) W. P. C. Barton</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Ramsebo Gölkullen, Hultsfred, Ramsebo Gölkullen, Hultsfred, Sm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>539552</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6348545</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Hultsfred</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Virserum</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>10 plantor, känd lokal</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>123354675</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57494</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Ramsebo Gölkullen, Hultsfred, Ramsebo Gölkullen, Hultsfred, Sm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>539542</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6348526</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Hultsfred</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Virserum</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>123352616</v>
+      </c>
+      <c r="B15" t="n">
+        <v>92233</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Ramsebo Gölkullen, Hultsfred, Ramsebo Gölkullen, Hultsfred, Sm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>539470</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6348569</v>
+      </c>
+      <c r="S15" t="n">
+        <v>15</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Hultsfred</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Virserum</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 37626-2024 artfynd.xlsx
+++ b/artfynd/A 37626-2024 artfynd.xlsx
@@ -913,10 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123352848</v>
+        <v>123352763</v>
       </c>
       <c r="B4" t="n">
-        <v>57631</v>
+        <v>98368</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,46 +925,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Ramsebo Gölkullen, Hultsfred, Ramsebo Gölkullen, Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>539517</v>
+        <v>539512</v>
       </c>
       <c r="R4" t="n">
-        <v>6348531</v>
+        <v>6348548</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1020,10 +1015,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123352763</v>
+        <v>123354675</v>
       </c>
       <c r="B5" t="n">
-        <v>98365</v>
+        <v>57497</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,41 +1027,46 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Ramsebo Gölkullen, Hultsfred, Ramsebo Gölkullen, Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>539512</v>
+        <v>539542</v>
       </c>
       <c r="R5" t="n">
-        <v>6348548</v>
+        <v>6348526</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1122,10 +1122,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123354802</v>
+        <v>123353224</v>
       </c>
       <c r="B6" t="n">
-        <v>100631</v>
+        <v>98368</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1134,25 +1134,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1162,13 +1162,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>539539</v>
+        <v>539470</v>
       </c>
       <c r="R6" t="n">
-        <v>6348519</v>
+        <v>6348541</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1227,7 +1227,7 @@
         <v>123354688</v>
       </c>
       <c r="B7" t="n">
-        <v>57631</v>
+        <v>57634</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1331,10 +1331,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123352575</v>
+        <v>123353749</v>
       </c>
       <c r="B8" t="n">
-        <v>92233</v>
+        <v>92236</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1371,10 +1371,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>539489</v>
+        <v>539463</v>
       </c>
       <c r="R8" t="n">
-        <v>6348577</v>
+        <v>6348578</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1433,10 +1433,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123353224</v>
+        <v>123352616</v>
       </c>
       <c r="B9" t="n">
-        <v>98365</v>
+        <v>92236</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1445,25 +1445,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1476,7 +1476,7 @@
         <v>539470</v>
       </c>
       <c r="R9" t="n">
-        <v>6348541</v>
+        <v>6348569</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1538,7 +1538,7 @@
         <v>123353834</v>
       </c>
       <c r="B10" t="n">
-        <v>92233</v>
+        <v>92236</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1642,10 +1642,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123353749</v>
+        <v>123352400</v>
       </c>
       <c r="B11" t="n">
-        <v>92233</v>
+        <v>57497</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1654,25 +1654,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1682,13 +1682,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>539463</v>
+        <v>539450</v>
       </c>
       <c r="R11" t="n">
-        <v>6348578</v>
+        <v>6348650</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1718,6 +1718,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1744,10 +1749,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123352400</v>
+        <v>123354802</v>
       </c>
       <c r="B12" t="n">
-        <v>57494</v>
+        <v>100634</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1756,25 +1761,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1784,13 +1789,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>539450</v>
+        <v>539539</v>
       </c>
       <c r="R12" t="n">
-        <v>6348650</v>
+        <v>6348519</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1820,11 +1825,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-03-21</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1851,10 +1851,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123354501</v>
+        <v>123352848</v>
       </c>
       <c r="B13" t="n">
-        <v>105432</v>
+        <v>57634</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1863,30 +1863,31 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>340</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ryl</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chimaphila umbellata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) W. P. C. Barton</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>10</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1895,13 +1896,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>539552</v>
+        <v>539517</v>
       </c>
       <c r="R13" t="n">
-        <v>6348545</v>
+        <v>6348531</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1931,11 +1932,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-03-21</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>10 plantor, känd lokal</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1962,10 +1958,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123354675</v>
+        <v>123354501</v>
       </c>
       <c r="B14" t="n">
-        <v>57494</v>
+        <v>105435</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1974,31 +1970,30 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>340</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ryl</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chimaphila umbellata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>(L.) W. P. C. Barton</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>10</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2007,13 +2002,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>539542</v>
+        <v>539552</v>
       </c>
       <c r="R14" t="n">
-        <v>6348526</v>
+        <v>6348545</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2043,6 +2038,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>10 plantor, känd lokal</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2069,10 +2069,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123352616</v>
+        <v>123352575</v>
       </c>
       <c r="B15" t="n">
-        <v>92233</v>
+        <v>92236</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2109,10 +2109,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>539470</v>
+        <v>539489</v>
       </c>
       <c r="R15" t="n">
-        <v>6348569</v>
+        <v>6348577</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>

--- a/artfynd/A 37626-2024 artfynd.xlsx
+++ b/artfynd/A 37626-2024 artfynd.xlsx
@@ -913,10 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123352763</v>
+        <v>123353834</v>
       </c>
       <c r="B4" t="n">
-        <v>98368</v>
+        <v>92238</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,25 +925,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -953,13 +953,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>539512</v>
+        <v>539458</v>
       </c>
       <c r="R4" t="n">
-        <v>6348548</v>
+        <v>6348572</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -989,6 +989,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>God förekomst, spridd i slänten</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1015,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123354675</v>
+        <v>123352575</v>
       </c>
       <c r="B5" t="n">
-        <v>57497</v>
+        <v>92238</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,46 +1032,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Ramsebo Gölkullen, Hultsfred, Ramsebo Gölkullen, Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>539542</v>
+        <v>539489</v>
       </c>
       <c r="R5" t="n">
-        <v>6348526</v>
+        <v>6348577</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1122,10 +1122,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123353224</v>
+        <v>123352616</v>
       </c>
       <c r="B6" t="n">
-        <v>98368</v>
+        <v>92238</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1134,25 +1134,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1165,7 +1165,7 @@
         <v>539470</v>
       </c>
       <c r="R6" t="n">
-        <v>6348541</v>
+        <v>6348569</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1224,10 +1224,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123354688</v>
+        <v>123353224</v>
       </c>
       <c r="B7" t="n">
-        <v>57634</v>
+        <v>98370</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1236,46 +1236,41 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Ramsebo Gölkullen, Hultsfred, Ramsebo Gölkullen, Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>539536</v>
+        <v>539470</v>
       </c>
       <c r="R7" t="n">
-        <v>6348529</v>
+        <v>6348541</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1331,10 +1326,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123353749</v>
+        <v>123354675</v>
       </c>
       <c r="B8" t="n">
-        <v>92236</v>
+        <v>57497</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1343,41 +1338,46 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Ramsebo Gölkullen, Hultsfred, Ramsebo Gölkullen, Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>539463</v>
+        <v>539542</v>
       </c>
       <c r="R8" t="n">
-        <v>6348578</v>
+        <v>6348526</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1433,10 +1433,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123352616</v>
+        <v>123354802</v>
       </c>
       <c r="B9" t="n">
-        <v>92236</v>
+        <v>100636</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1449,21 +1449,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>222498</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1473,13 +1473,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>539470</v>
+        <v>539539</v>
       </c>
       <c r="R9" t="n">
-        <v>6348569</v>
+        <v>6348519</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1535,10 +1535,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123353834</v>
+        <v>123354501</v>
       </c>
       <c r="B10" t="n">
-        <v>92236</v>
+        <v>105437</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1547,41 +1547,45 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>340</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ryl</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chimaphila umbellata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) W. P. C. Barton</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Ramsebo Gölkullen, Hultsfred, Ramsebo Gölkullen, Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>539458</v>
+        <v>539552</v>
       </c>
       <c r="R10" t="n">
-        <v>6348572</v>
+        <v>6348545</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1615,7 +1619,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>God förekomst, spridd i slänten</t>
+          <t>10 plantor, känd lokal</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1749,10 +1753,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123354802</v>
+        <v>123352763</v>
       </c>
       <c r="B12" t="n">
-        <v>100634</v>
+        <v>98370</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1761,25 +1765,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1789,13 +1793,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>539539</v>
+        <v>539512</v>
       </c>
       <c r="R12" t="n">
-        <v>6348519</v>
+        <v>6348548</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1851,10 +1855,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123352848</v>
+        <v>123353749</v>
       </c>
       <c r="B13" t="n">
-        <v>57634</v>
+        <v>92238</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1863,46 +1867,41 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Ramsebo Gölkullen, Hultsfred, Ramsebo Gölkullen, Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>539517</v>
+        <v>539463</v>
       </c>
       <c r="R13" t="n">
-        <v>6348531</v>
+        <v>6348578</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1958,10 +1957,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123354501</v>
+        <v>123354688</v>
       </c>
       <c r="B14" t="n">
-        <v>105435</v>
+        <v>57634</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1970,30 +1969,31 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>340</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ryl</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chimaphila umbellata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) W. P. C. Barton</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>10</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2002,13 +2002,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>539552</v>
+        <v>539536</v>
       </c>
       <c r="R14" t="n">
-        <v>6348545</v>
+        <v>6348529</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2038,11 +2038,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-03-21</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>10 plantor, känd lokal</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2069,10 +2064,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123352575</v>
+        <v>123352848</v>
       </c>
       <c r="B15" t="n">
-        <v>92236</v>
+        <v>57634</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2081,41 +2076,46 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Ramsebo Gölkullen, Hultsfred, Ramsebo Gölkullen, Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>539489</v>
+        <v>539517</v>
       </c>
       <c r="R15" t="n">
-        <v>6348577</v>
+        <v>6348531</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>

--- a/artfynd/A 37626-2024 artfynd.xlsx
+++ b/artfynd/A 37626-2024 artfynd.xlsx
@@ -913,10 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123353834</v>
+        <v>123354501</v>
       </c>
       <c r="B4" t="n">
-        <v>92238</v>
+        <v>105443</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,41 +925,45 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>340</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ryl</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chimaphila umbellata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) W. P. C. Barton</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Ramsebo Gölkullen, Hultsfred, Ramsebo Gölkullen, Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>539458</v>
+        <v>539552</v>
       </c>
       <c r="R4" t="n">
-        <v>6348572</v>
+        <v>6348545</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -993,7 +997,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>God förekomst, spridd i slänten</t>
+          <t>10 plantor, känd lokal</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,10 +1024,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123352575</v>
+        <v>123354802</v>
       </c>
       <c r="B5" t="n">
-        <v>92238</v>
+        <v>100642</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,21 +1040,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>222498</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1060,13 +1064,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>539489</v>
+        <v>539539</v>
       </c>
       <c r="R5" t="n">
-        <v>6348577</v>
+        <v>6348519</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1122,10 +1126,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123352616</v>
+        <v>123354688</v>
       </c>
       <c r="B6" t="n">
-        <v>92238</v>
+        <v>57634</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1134,41 +1138,46 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Ramsebo Gölkullen, Hultsfred, Ramsebo Gölkullen, Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>539470</v>
+        <v>539536</v>
       </c>
       <c r="R6" t="n">
-        <v>6348569</v>
+        <v>6348529</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1224,10 +1233,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123353224</v>
+        <v>123352616</v>
       </c>
       <c r="B7" t="n">
-        <v>98370</v>
+        <v>92244</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1236,25 +1245,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1267,7 +1276,7 @@
         <v>539470</v>
       </c>
       <c r="R7" t="n">
-        <v>6348541</v>
+        <v>6348569</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1326,10 +1335,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123354675</v>
+        <v>123352763</v>
       </c>
       <c r="B8" t="n">
-        <v>57497</v>
+        <v>98376</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1338,46 +1347,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Ramsebo Gölkullen, Hultsfred, Ramsebo Gölkullen, Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>539542</v>
+        <v>539512</v>
       </c>
       <c r="R8" t="n">
-        <v>6348526</v>
+        <v>6348548</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1433,10 +1437,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123354802</v>
+        <v>123353749</v>
       </c>
       <c r="B9" t="n">
-        <v>100636</v>
+        <v>92244</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1449,21 +1453,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1473,13 +1477,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>539539</v>
+        <v>539463</v>
       </c>
       <c r="R9" t="n">
-        <v>6348519</v>
+        <v>6348578</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1535,10 +1539,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123354501</v>
+        <v>123354675</v>
       </c>
       <c r="B10" t="n">
-        <v>105437</v>
+        <v>57497</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1547,30 +1551,31 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>340</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ryl</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chimaphila umbellata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) W. P. C. Barton</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>10</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1579,13 +1584,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>539552</v>
+        <v>539542</v>
       </c>
       <c r="R10" t="n">
-        <v>6348545</v>
+        <v>6348526</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1615,11 +1620,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-03-21</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>10 plantor, känd lokal</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1646,10 +1646,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123352400</v>
+        <v>123352848</v>
       </c>
       <c r="B11" t="n">
-        <v>57497</v>
+        <v>57634</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1662,37 +1662,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Ramsebo Gölkullen, Hultsfred, Ramsebo Gölkullen, Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>539450</v>
+        <v>539517</v>
       </c>
       <c r="R11" t="n">
-        <v>6348650</v>
+        <v>6348531</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1722,11 +1727,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-03-21</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1753,10 +1753,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123352763</v>
+        <v>123353834</v>
       </c>
       <c r="B12" t="n">
-        <v>98370</v>
+        <v>92244</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1765,25 +1765,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1793,13 +1793,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>539512</v>
+        <v>539458</v>
       </c>
       <c r="R12" t="n">
-        <v>6348548</v>
+        <v>6348572</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1829,6 +1829,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>God förekomst, spridd i slänten</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1855,10 +1860,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123353749</v>
+        <v>123352575</v>
       </c>
       <c r="B13" t="n">
-        <v>92238</v>
+        <v>92244</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1895,10 +1900,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>539463</v>
+        <v>539489</v>
       </c>
       <c r="R13" t="n">
-        <v>6348578</v>
+        <v>6348577</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1957,10 +1962,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123354688</v>
+        <v>123353224</v>
       </c>
       <c r="B14" t="n">
-        <v>57634</v>
+        <v>98376</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1969,46 +1974,41 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Ramsebo Gölkullen, Hultsfred, Ramsebo Gölkullen, Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>539536</v>
+        <v>539470</v>
       </c>
       <c r="R14" t="n">
-        <v>6348529</v>
+        <v>6348541</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2064,10 +2064,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123352848</v>
+        <v>123352400</v>
       </c>
       <c r="B15" t="n">
-        <v>57634</v>
+        <v>57497</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2080,42 +2080,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Ramsebo Gölkullen, Hultsfred, Ramsebo Gölkullen, Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>539517</v>
+        <v>539450</v>
       </c>
       <c r="R15" t="n">
-        <v>6348531</v>
+        <v>6348650</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2145,6 +2140,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 37626-2024 artfynd.xlsx
+++ b/artfynd/A 37626-2024 artfynd.xlsx
@@ -913,10 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123354802</v>
+        <v>123352616</v>
       </c>
       <c r="B4" t="n">
-        <v>100645</v>
+        <v>92264</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -929,21 +929,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -953,13 +953,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>539539</v>
+        <v>539470</v>
       </c>
       <c r="R4" t="n">
-        <v>6348519</v>
+        <v>6348569</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1015,10 +1015,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123353224</v>
+        <v>123352575</v>
       </c>
       <c r="B5" t="n">
-        <v>98379</v>
+        <v>92264</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,25 +1027,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1055,10 +1055,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>539470</v>
+        <v>539489</v>
       </c>
       <c r="R5" t="n">
-        <v>6348541</v>
+        <v>6348577</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1117,10 +1117,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123354501</v>
+        <v>123352400</v>
       </c>
       <c r="B6" t="n">
-        <v>105446</v>
+        <v>57503</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1129,42 +1129,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>340</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ryl</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chimaphila umbellata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) W. P. C. Barton</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Ramsebo Gölkullen, Hultsfred, Ramsebo Gölkullen, Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>539552</v>
+        <v>539450</v>
       </c>
       <c r="R6" t="n">
-        <v>6348545</v>
+        <v>6348650</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1201,7 +1197,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>10 plantor, känd lokal</t>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1228,10 +1224,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123353749</v>
+        <v>123354675</v>
       </c>
       <c r="B7" t="n">
-        <v>92247</v>
+        <v>57503</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1240,41 +1236,46 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Ramsebo Gölkullen, Hultsfred, Ramsebo Gölkullen, Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>539463</v>
+        <v>539542</v>
       </c>
       <c r="R7" t="n">
-        <v>6348578</v>
+        <v>6348526</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1330,10 +1331,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123352400</v>
+        <v>123353834</v>
       </c>
       <c r="B8" t="n">
-        <v>57497</v>
+        <v>92264</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1342,25 +1343,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1370,13 +1371,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>539450</v>
+        <v>539458</v>
       </c>
       <c r="R8" t="n">
-        <v>6348650</v>
+        <v>6348572</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1410,7 +1411,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Födosökshack</t>
+          <t>God förekomst, spridd i slänten</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1437,10 +1438,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123354675</v>
+        <v>123353749</v>
       </c>
       <c r="B9" t="n">
-        <v>57497</v>
+        <v>92264</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1449,46 +1450,41 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Ramsebo Gölkullen, Hultsfred, Ramsebo Gölkullen, Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>539542</v>
+        <v>539463</v>
       </c>
       <c r="R9" t="n">
-        <v>6348526</v>
+        <v>6348578</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1544,10 +1540,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123352575</v>
+        <v>123352763</v>
       </c>
       <c r="B10" t="n">
-        <v>92247</v>
+        <v>98396</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1556,25 +1552,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1584,13 +1580,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>539489</v>
+        <v>539512</v>
       </c>
       <c r="R10" t="n">
-        <v>6348577</v>
+        <v>6348548</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1646,10 +1642,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123352763</v>
+        <v>123354501</v>
       </c>
       <c r="B11" t="n">
-        <v>98379</v>
+        <v>105463</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1658,38 +1654,42 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>340</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ryl</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chimaphila umbellata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) W. P. C. Barton</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Ramsebo Gölkullen, Hultsfred, Ramsebo Gölkullen, Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>539512</v>
+        <v>539552</v>
       </c>
       <c r="R11" t="n">
-        <v>6348548</v>
+        <v>6348545</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1722,6 +1722,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>10 plantor, känd lokal</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1748,10 +1753,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123353834</v>
+        <v>123354802</v>
       </c>
       <c r="B12" t="n">
-        <v>92247</v>
+        <v>100662</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1764,21 +1769,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>222498</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1788,10 +1793,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>539458</v>
+        <v>539539</v>
       </c>
       <c r="R12" t="n">
-        <v>6348572</v>
+        <v>6348519</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1824,11 +1829,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-03-21</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>God förekomst, spridd i slänten</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1855,10 +1855,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123354688</v>
+        <v>123352848</v>
       </c>
       <c r="B13" t="n">
-        <v>57634</v>
+        <v>57640</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1900,10 +1900,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>539536</v>
+        <v>539517</v>
       </c>
       <c r="R13" t="n">
-        <v>6348529</v>
+        <v>6348531</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1962,10 +1962,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123352616</v>
+        <v>123353224</v>
       </c>
       <c r="B14" t="n">
-        <v>92247</v>
+        <v>98396</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1974,25 +1974,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2005,7 +2005,7 @@
         <v>539470</v>
       </c>
       <c r="R14" t="n">
-        <v>6348569</v>
+        <v>6348541</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2064,10 +2064,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123352848</v>
+        <v>123354688</v>
       </c>
       <c r="B15" t="n">
-        <v>57634</v>
+        <v>57640</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2109,10 +2109,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>539517</v>
+        <v>539536</v>
       </c>
       <c r="R15" t="n">
-        <v>6348531</v>
+        <v>6348529</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>

--- a/artfynd/A 37626-2024 artfynd.xlsx
+++ b/artfynd/A 37626-2024 artfynd.xlsx
@@ -1015,10 +1015,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123352575</v>
+        <v>123352400</v>
       </c>
       <c r="B5" t="n">
-        <v>92264</v>
+        <v>57503</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,25 +1027,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1055,13 +1055,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>539489</v>
+        <v>539450</v>
       </c>
       <c r="R5" t="n">
-        <v>6348577</v>
+        <v>6348650</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1091,6 +1091,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1117,10 +1122,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123352400</v>
+        <v>123352575</v>
       </c>
       <c r="B6" t="n">
-        <v>57503</v>
+        <v>92264</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1129,25 +1134,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1157,13 +1162,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>539450</v>
+        <v>539489</v>
       </c>
       <c r="R6" t="n">
-        <v>6348650</v>
+        <v>6348577</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1193,11 +1198,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-03-21</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 37626-2024 artfynd.xlsx
+++ b/artfynd/A 37626-2024 artfynd.xlsx
@@ -913,10 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123352616</v>
+        <v>123353834</v>
       </c>
       <c r="B4" t="n">
-        <v>92264</v>
+        <v>92269</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -953,13 +953,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>539470</v>
+        <v>539458</v>
       </c>
       <c r="R4" t="n">
-        <v>6348569</v>
+        <v>6348572</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -989,6 +989,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>God förekomst, spridd i slänten</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1015,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123352400</v>
+        <v>123352575</v>
       </c>
       <c r="B5" t="n">
-        <v>57503</v>
+        <v>92269</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,25 +1032,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1055,13 +1060,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>539450</v>
+        <v>539489</v>
       </c>
       <c r="R5" t="n">
-        <v>6348650</v>
+        <v>6348577</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1091,11 +1096,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-03-21</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1122,10 +1122,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123352575</v>
+        <v>123352616</v>
       </c>
       <c r="B6" t="n">
-        <v>92264</v>
+        <v>92269</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1162,10 +1162,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>539489</v>
+        <v>539470</v>
       </c>
       <c r="R6" t="n">
-        <v>6348577</v>
+        <v>6348569</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1224,10 +1224,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123354675</v>
+        <v>123354501</v>
       </c>
       <c r="B7" t="n">
-        <v>57503</v>
+        <v>105479</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1236,31 +1236,30 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>340</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ryl</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chimaphila umbellata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>(L.) W. P. C. Barton</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>10</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1269,13 +1268,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>539542</v>
+        <v>539552</v>
       </c>
       <c r="R7" t="n">
-        <v>6348526</v>
+        <v>6348545</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1305,6 +1304,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>10 plantor, känd lokal</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1331,10 +1335,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123353834</v>
+        <v>123353224</v>
       </c>
       <c r="B8" t="n">
-        <v>92264</v>
+        <v>98502</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1343,25 +1347,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1371,13 +1375,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>539458</v>
+        <v>539470</v>
       </c>
       <c r="R8" t="n">
-        <v>6348572</v>
+        <v>6348541</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1407,11 +1411,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-03-21</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>God förekomst, spridd i slänten</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1438,10 +1437,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123353749</v>
+        <v>123352400</v>
       </c>
       <c r="B9" t="n">
-        <v>92264</v>
+        <v>57506</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1450,25 +1449,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1478,13 +1477,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>539463</v>
+        <v>539450</v>
       </c>
       <c r="R9" t="n">
-        <v>6348578</v>
+        <v>6348650</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1514,6 +1513,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1540,10 +1544,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123352763</v>
+        <v>123352848</v>
       </c>
       <c r="B10" t="n">
-        <v>98396</v>
+        <v>57643</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1552,41 +1556,46 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Ramsebo Gölkullen, Hultsfred, Ramsebo Gölkullen, Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>539512</v>
+        <v>539517</v>
       </c>
       <c r="R10" t="n">
-        <v>6348548</v>
+        <v>6348531</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1642,10 +1651,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123354501</v>
+        <v>123352763</v>
       </c>
       <c r="B11" t="n">
-        <v>105463</v>
+        <v>98502</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1654,42 +1663,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>340</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ryl</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chimaphila umbellata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) W. P. C. Barton</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Ramsebo Gölkullen, Hultsfred, Ramsebo Gölkullen, Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>539552</v>
+        <v>539512</v>
       </c>
       <c r="R11" t="n">
-        <v>6348545</v>
+        <v>6348548</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1722,11 +1727,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-03-21</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>10 plantor, känd lokal</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1753,10 +1753,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123354802</v>
+        <v>123354688</v>
       </c>
       <c r="B12" t="n">
-        <v>100662</v>
+        <v>57643</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1765,38 +1765,43 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222498</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Ramsebo Gölkullen, Hultsfred, Ramsebo Gölkullen, Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>539539</v>
+        <v>539536</v>
       </c>
       <c r="R12" t="n">
-        <v>6348519</v>
+        <v>6348529</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1855,10 +1860,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123352848</v>
+        <v>123354675</v>
       </c>
       <c r="B13" t="n">
-        <v>57640</v>
+        <v>57506</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1871,27 +1876,27 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1900,10 +1905,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>539517</v>
+        <v>539542</v>
       </c>
       <c r="R13" t="n">
-        <v>6348531</v>
+        <v>6348526</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1962,10 +1967,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123353224</v>
+        <v>123354802</v>
       </c>
       <c r="B14" t="n">
-        <v>98396</v>
+        <v>100680</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1974,25 +1979,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2002,13 +2007,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>539470</v>
+        <v>539539</v>
       </c>
       <c r="R14" t="n">
-        <v>6348541</v>
+        <v>6348519</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2064,10 +2069,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123354688</v>
+        <v>123353749</v>
       </c>
       <c r="B15" t="n">
-        <v>57640</v>
+        <v>92269</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2076,46 +2081,41 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Ramsebo Gölkullen, Hultsfred, Ramsebo Gölkullen, Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>539536</v>
+        <v>539463</v>
       </c>
       <c r="R15" t="n">
-        <v>6348529</v>
+        <v>6348578</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>

--- a/artfynd/A 37626-2024 artfynd.xlsx
+++ b/artfynd/A 37626-2024 artfynd.xlsx
@@ -913,10 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123353834</v>
+        <v>123353749</v>
       </c>
       <c r="B4" t="n">
-        <v>92269</v>
+        <v>92271</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -953,13 +953,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>539458</v>
+        <v>539463</v>
       </c>
       <c r="R4" t="n">
-        <v>6348572</v>
+        <v>6348578</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -989,11 +989,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-21</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>God förekomst, spridd i slänten</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,10 +1015,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123352575</v>
+        <v>123352400</v>
       </c>
       <c r="B5" t="n">
-        <v>92269</v>
+        <v>57507</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,25 +1027,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1060,13 +1055,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>539489</v>
+        <v>539450</v>
       </c>
       <c r="R5" t="n">
-        <v>6348577</v>
+        <v>6348650</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1096,6 +1091,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1122,10 +1122,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123352616</v>
+        <v>123354688</v>
       </c>
       <c r="B6" t="n">
-        <v>92269</v>
+        <v>57644</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1134,41 +1134,46 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Ramsebo Gölkullen, Hultsfred, Ramsebo Gölkullen, Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>539470</v>
+        <v>539536</v>
       </c>
       <c r="R6" t="n">
-        <v>6348569</v>
+        <v>6348529</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1224,10 +1229,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123354501</v>
+        <v>123352848</v>
       </c>
       <c r="B7" t="n">
-        <v>105479</v>
+        <v>57644</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1236,30 +1241,31 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>340</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ryl</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chimaphila umbellata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) W. P. C. Barton</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>10</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1268,13 +1274,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>539552</v>
+        <v>539517</v>
       </c>
       <c r="R7" t="n">
-        <v>6348545</v>
+        <v>6348531</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1304,11 +1310,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-03-21</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>10 plantor, känd lokal</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1335,10 +1336,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123353224</v>
+        <v>123352616</v>
       </c>
       <c r="B8" t="n">
-        <v>98502</v>
+        <v>92271</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1347,25 +1348,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1378,7 +1379,7 @@
         <v>539470</v>
       </c>
       <c r="R8" t="n">
-        <v>6348541</v>
+        <v>6348569</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1437,10 +1438,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123352400</v>
+        <v>123354675</v>
       </c>
       <c r="B9" t="n">
-        <v>57506</v>
+        <v>57507</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1471,19 +1472,24 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Ramsebo Gölkullen, Hultsfred, Ramsebo Gölkullen, Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>539450</v>
+        <v>539542</v>
       </c>
       <c r="R9" t="n">
-        <v>6348650</v>
+        <v>6348526</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1513,11 +1519,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-03-21</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1544,10 +1545,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123352848</v>
+        <v>123352763</v>
       </c>
       <c r="B10" t="n">
-        <v>57643</v>
+        <v>98504</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1556,46 +1557,41 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Ramsebo Gölkullen, Hultsfred, Ramsebo Gölkullen, Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>539517</v>
+        <v>539512</v>
       </c>
       <c r="R10" t="n">
-        <v>6348531</v>
+        <v>6348548</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1651,10 +1647,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123352763</v>
+        <v>123353224</v>
       </c>
       <c r="B11" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1691,13 +1687,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>539512</v>
+        <v>539470</v>
       </c>
       <c r="R11" t="n">
-        <v>6348548</v>
+        <v>6348541</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1753,10 +1749,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123354688</v>
+        <v>123354501</v>
       </c>
       <c r="B12" t="n">
-        <v>57643</v>
+        <v>105481</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1765,31 +1761,30 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>340</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ryl</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chimaphila umbellata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>(L.) W. P. C. Barton</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>10</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1798,13 +1793,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>539536</v>
+        <v>539552</v>
       </c>
       <c r="R12" t="n">
-        <v>6348529</v>
+        <v>6348545</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1834,6 +1829,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>10 plantor, känd lokal</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1860,10 +1860,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123354675</v>
+        <v>123352575</v>
       </c>
       <c r="B13" t="n">
-        <v>57506</v>
+        <v>92271</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1872,46 +1872,41 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Ramsebo Gölkullen, Hultsfred, Ramsebo Gölkullen, Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>539542</v>
+        <v>539489</v>
       </c>
       <c r="R13" t="n">
-        <v>6348526</v>
+        <v>6348577</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1970,7 +1965,7 @@
         <v>123354802</v>
       </c>
       <c r="B14" t="n">
-        <v>100680</v>
+        <v>100682</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2069,10 +2064,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123353749</v>
+        <v>123353834</v>
       </c>
       <c r="B15" t="n">
-        <v>92269</v>
+        <v>92271</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2109,13 +2104,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>539463</v>
+        <v>539458</v>
       </c>
       <c r="R15" t="n">
-        <v>6348578</v>
+        <v>6348572</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2145,6 +2140,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>God förekomst, spridd i slänten</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 37626-2024 artfynd.xlsx
+++ b/artfynd/A 37626-2024 artfynd.xlsx
@@ -913,10 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123353749</v>
+        <v>123352848</v>
       </c>
       <c r="B4" t="n">
-        <v>92271</v>
+        <v>57644</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,41 +925,46 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Ramsebo Gölkullen, Hultsfred, Ramsebo Gölkullen, Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>539463</v>
+        <v>539517</v>
       </c>
       <c r="R4" t="n">
-        <v>6348578</v>
+        <v>6348531</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1015,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123352400</v>
+        <v>123352616</v>
       </c>
       <c r="B5" t="n">
-        <v>57507</v>
+        <v>92271</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,25 +1032,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1055,13 +1060,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>539450</v>
+        <v>539470</v>
       </c>
       <c r="R5" t="n">
-        <v>6348650</v>
+        <v>6348569</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1091,11 +1096,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-03-21</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1122,10 +1122,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123354688</v>
+        <v>123353834</v>
       </c>
       <c r="B6" t="n">
-        <v>57644</v>
+        <v>92271</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1134,43 +1134,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Ramsebo Gölkullen, Hultsfred, Ramsebo Gölkullen, Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>539536</v>
+        <v>539458</v>
       </c>
       <c r="R6" t="n">
-        <v>6348529</v>
+        <v>6348572</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1203,6 +1198,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>God förekomst, spridd i slänten</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1229,10 +1229,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123352848</v>
+        <v>123353224</v>
       </c>
       <c r="B7" t="n">
-        <v>57644</v>
+        <v>98079</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1241,46 +1241,41 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Ramsebo Gölkullen, Hultsfred, Ramsebo Gölkullen, Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>539517</v>
+        <v>539470</v>
       </c>
       <c r="R7" t="n">
-        <v>6348531</v>
+        <v>6348541</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1336,7 +1331,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123352616</v>
+        <v>123352575</v>
       </c>
       <c r="B8" t="n">
         <v>92271</v>
@@ -1376,10 +1371,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>539470</v>
+        <v>539489</v>
       </c>
       <c r="R8" t="n">
-        <v>6348569</v>
+        <v>6348577</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1438,10 +1433,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123354675</v>
+        <v>123354501</v>
       </c>
       <c r="B9" t="n">
-        <v>57507</v>
+        <v>105056</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1450,31 +1445,30 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>340</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ryl</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chimaphila umbellata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>(L.) W. P. C. Barton</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>10</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1483,13 +1477,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>539542</v>
+        <v>539552</v>
       </c>
       <c r="R9" t="n">
-        <v>6348526</v>
+        <v>6348545</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1519,6 +1513,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>10 plantor, känd lokal</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1545,10 +1544,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123352763</v>
+        <v>123354688</v>
       </c>
       <c r="B10" t="n">
-        <v>98504</v>
+        <v>57644</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1557,41 +1556,46 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Ramsebo Gölkullen, Hultsfred, Ramsebo Gölkullen, Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>539512</v>
+        <v>539536</v>
       </c>
       <c r="R10" t="n">
-        <v>6348548</v>
+        <v>6348529</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1647,10 +1651,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123353224</v>
+        <v>123352400</v>
       </c>
       <c r="B11" t="n">
-        <v>98504</v>
+        <v>57507</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1659,25 +1663,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1687,13 +1691,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>539470</v>
+        <v>539450</v>
       </c>
       <c r="R11" t="n">
-        <v>6348541</v>
+        <v>6348650</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1723,6 +1727,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1749,10 +1758,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123354501</v>
+        <v>123353749</v>
       </c>
       <c r="B12" t="n">
-        <v>105481</v>
+        <v>92271</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1761,45 +1770,41 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>340</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ryl</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chimaphila umbellata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) W. P. C. Barton</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Ramsebo Gölkullen, Hultsfred, Ramsebo Gölkullen, Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>539552</v>
+        <v>539463</v>
       </c>
       <c r="R12" t="n">
-        <v>6348545</v>
+        <v>6348578</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1829,11 +1834,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-03-21</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>10 plantor, känd lokal</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1860,10 +1860,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123352575</v>
+        <v>123354675</v>
       </c>
       <c r="B13" t="n">
-        <v>92271</v>
+        <v>57507</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1872,41 +1872,46 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Ramsebo Gölkullen, Hultsfred, Ramsebo Gölkullen, Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>539489</v>
+        <v>539542</v>
       </c>
       <c r="R13" t="n">
-        <v>6348577</v>
+        <v>6348526</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1965,7 +1970,7 @@
         <v>123354802</v>
       </c>
       <c r="B14" t="n">
-        <v>100682</v>
+        <v>100257</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2064,10 +2069,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123353834</v>
+        <v>123352763</v>
       </c>
       <c r="B15" t="n">
-        <v>92271</v>
+        <v>98079</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2076,25 +2081,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2104,13 +2109,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>539458</v>
+        <v>539512</v>
       </c>
       <c r="R15" t="n">
-        <v>6348572</v>
+        <v>6348548</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2140,11 +2145,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-03-21</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>God förekomst, spridd i slänten</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 37626-2024 artfynd.xlsx
+++ b/artfynd/A 37626-2024 artfynd.xlsx
@@ -913,10 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123352848</v>
+        <v>123353224</v>
       </c>
       <c r="B4" t="n">
-        <v>57644</v>
+        <v>98079</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,46 +925,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Ramsebo Gölkullen, Hultsfred, Ramsebo Gölkullen, Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>539517</v>
+        <v>539470</v>
       </c>
       <c r="R4" t="n">
-        <v>6348531</v>
+        <v>6348541</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1020,10 +1015,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123352616</v>
+        <v>123354501</v>
       </c>
       <c r="B5" t="n">
-        <v>92271</v>
+        <v>105056</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,41 +1027,45 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>340</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ryl</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chimaphila umbellata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) W. P. C. Barton</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Ramsebo Gölkullen, Hultsfred, Ramsebo Gölkullen, Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>539470</v>
+        <v>539552</v>
       </c>
       <c r="R5" t="n">
-        <v>6348569</v>
+        <v>6348545</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1096,6 +1095,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>10 plantor, känd lokal</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1122,10 +1126,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123353834</v>
+        <v>123354675</v>
       </c>
       <c r="B6" t="n">
-        <v>92271</v>
+        <v>57507</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1134,38 +1138,43 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Ramsebo Gölkullen, Hultsfred, Ramsebo Gölkullen, Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>539458</v>
+        <v>539542</v>
       </c>
       <c r="R6" t="n">
-        <v>6348572</v>
+        <v>6348526</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1198,11 +1207,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-03-21</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>God förekomst, spridd i slänten</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1229,10 +1233,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123353224</v>
+        <v>123354688</v>
       </c>
       <c r="B7" t="n">
-        <v>98079</v>
+        <v>57644</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1241,41 +1245,46 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Ramsebo Gölkullen, Hultsfred, Ramsebo Gölkullen, Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>539470</v>
+        <v>539536</v>
       </c>
       <c r="R7" t="n">
-        <v>6348541</v>
+        <v>6348529</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1331,7 +1340,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123352575</v>
+        <v>123352616</v>
       </c>
       <c r="B8" t="n">
         <v>92271</v>
@@ -1371,10 +1380,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>539489</v>
+        <v>539470</v>
       </c>
       <c r="R8" t="n">
-        <v>6348577</v>
+        <v>6348569</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1433,10 +1442,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123354501</v>
+        <v>123354802</v>
       </c>
       <c r="B9" t="n">
-        <v>105056</v>
+        <v>100257</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1445,45 +1454,41 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>340</v>
+        <v>222498</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ryl</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chimaphila umbellata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) W. P. C. Barton</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Ramsebo Gölkullen, Hultsfred, Ramsebo Gölkullen, Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>539552</v>
+        <v>539539</v>
       </c>
       <c r="R9" t="n">
-        <v>6348545</v>
+        <v>6348519</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1513,11 +1518,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-03-21</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>10 plantor, känd lokal</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1544,7 +1544,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123354688</v>
+        <v>123352848</v>
       </c>
       <c r="B10" t="n">
         <v>57644</v>
@@ -1589,10 +1589,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>539536</v>
+        <v>539517</v>
       </c>
       <c r="R10" t="n">
-        <v>6348529</v>
+        <v>6348531</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1651,10 +1651,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123352400</v>
+        <v>123352763</v>
       </c>
       <c r="B11" t="n">
-        <v>57507</v>
+        <v>98079</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1663,25 +1663,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1691,10 +1691,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>539450</v>
+        <v>539512</v>
       </c>
       <c r="R11" t="n">
-        <v>6348650</v>
+        <v>6348548</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1727,11 +1727,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-03-21</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1758,7 +1753,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123353749</v>
+        <v>123352575</v>
       </c>
       <c r="B12" t="n">
         <v>92271</v>
@@ -1798,10 +1793,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>539463</v>
+        <v>539489</v>
       </c>
       <c r="R12" t="n">
-        <v>6348578</v>
+        <v>6348577</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1860,10 +1855,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123354675</v>
+        <v>123353749</v>
       </c>
       <c r="B13" t="n">
-        <v>57507</v>
+        <v>92271</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1872,46 +1867,41 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Ramsebo Gölkullen, Hultsfred, Ramsebo Gölkullen, Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>539542</v>
+        <v>539463</v>
       </c>
       <c r="R13" t="n">
-        <v>6348526</v>
+        <v>6348578</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1967,10 +1957,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123354802</v>
+        <v>123352400</v>
       </c>
       <c r="B14" t="n">
-        <v>100257</v>
+        <v>57507</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1979,25 +1969,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2007,13 +1997,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>539539</v>
+        <v>539450</v>
       </c>
       <c r="R14" t="n">
-        <v>6348519</v>
+        <v>6348650</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2043,6 +2033,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2069,10 +2064,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123352763</v>
+        <v>123353834</v>
       </c>
       <c r="B15" t="n">
-        <v>98079</v>
+        <v>92271</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2081,25 +2076,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2109,13 +2104,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>539512</v>
+        <v>539458</v>
       </c>
       <c r="R15" t="n">
-        <v>6348548</v>
+        <v>6348572</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2145,6 +2140,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>God förekomst, spridd i slänten</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 37626-2024 artfynd.xlsx
+++ b/artfynd/A 37626-2024 artfynd.xlsx
@@ -913,10 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123353224</v>
+        <v>123354688</v>
       </c>
       <c r="B4" t="n">
-        <v>98079</v>
+        <v>57644</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,41 +925,46 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Ramsebo Gölkullen, Hultsfred, Ramsebo Gölkullen, Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>539470</v>
+        <v>539536</v>
       </c>
       <c r="R4" t="n">
-        <v>6348541</v>
+        <v>6348529</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1126,10 +1131,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123354675</v>
+        <v>123353224</v>
       </c>
       <c r="B6" t="n">
-        <v>57507</v>
+        <v>98079</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1138,46 +1143,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Ramsebo Gölkullen, Hultsfred, Ramsebo Gölkullen, Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>539542</v>
+        <v>539470</v>
       </c>
       <c r="R6" t="n">
-        <v>6348526</v>
+        <v>6348541</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1233,10 +1233,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123354688</v>
+        <v>123352616</v>
       </c>
       <c r="B7" t="n">
-        <v>57644</v>
+        <v>92271</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1245,46 +1245,41 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Ramsebo Gölkullen, Hultsfred, Ramsebo Gölkullen, Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>539536</v>
+        <v>539470</v>
       </c>
       <c r="R7" t="n">
-        <v>6348529</v>
+        <v>6348569</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1340,10 +1335,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123352616</v>
+        <v>123352848</v>
       </c>
       <c r="B8" t="n">
-        <v>92271</v>
+        <v>57644</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1352,41 +1347,46 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Ramsebo Gölkullen, Hultsfred, Ramsebo Gölkullen, Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>539470</v>
+        <v>539517</v>
       </c>
       <c r="R8" t="n">
-        <v>6348569</v>
+        <v>6348531</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1442,10 +1442,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123354802</v>
+        <v>123352763</v>
       </c>
       <c r="B9" t="n">
-        <v>100257</v>
+        <v>98079</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1454,25 +1454,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1482,13 +1482,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>539539</v>
+        <v>539512</v>
       </c>
       <c r="R9" t="n">
-        <v>6348519</v>
+        <v>6348548</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1544,10 +1544,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123352848</v>
+        <v>123354675</v>
       </c>
       <c r="B10" t="n">
-        <v>57644</v>
+        <v>57507</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1560,27 +1560,27 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1589,10 +1589,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>539517</v>
+        <v>539542</v>
       </c>
       <c r="R10" t="n">
-        <v>6348531</v>
+        <v>6348526</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1651,10 +1651,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123352763</v>
+        <v>123353834</v>
       </c>
       <c r="B11" t="n">
-        <v>98079</v>
+        <v>92271</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1663,25 +1663,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1691,13 +1691,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>539512</v>
+        <v>539458</v>
       </c>
       <c r="R11" t="n">
-        <v>6348548</v>
+        <v>6348572</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1727,6 +1727,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>God förekomst, spridd i slänten</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1753,7 +1758,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123352575</v>
+        <v>123353749</v>
       </c>
       <c r="B12" t="n">
         <v>92271</v>
@@ -1793,10 +1798,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>539489</v>
+        <v>539463</v>
       </c>
       <c r="R12" t="n">
-        <v>6348577</v>
+        <v>6348578</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1855,10 +1860,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123353749</v>
+        <v>123352400</v>
       </c>
       <c r="B13" t="n">
-        <v>92271</v>
+        <v>57507</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1867,25 +1872,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1895,13 +1900,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>539463</v>
+        <v>539450</v>
       </c>
       <c r="R13" t="n">
-        <v>6348578</v>
+        <v>6348650</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1931,6 +1936,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1957,10 +1967,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123352400</v>
+        <v>123354802</v>
       </c>
       <c r="B14" t="n">
-        <v>57507</v>
+        <v>100257</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1969,25 +1979,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1997,13 +2007,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>539450</v>
+        <v>539539</v>
       </c>
       <c r="R14" t="n">
-        <v>6348650</v>
+        <v>6348519</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2033,11 +2043,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-03-21</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2064,7 +2069,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123353834</v>
+        <v>123352575</v>
       </c>
       <c r="B15" t="n">
         <v>92271</v>
@@ -2104,13 +2109,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>539458</v>
+        <v>539489</v>
       </c>
       <c r="R15" t="n">
-        <v>6348572</v>
+        <v>6348577</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2140,11 +2145,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-03-21</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>God förekomst, spridd i slänten</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 37626-2024 artfynd.xlsx
+++ b/artfynd/A 37626-2024 artfynd.xlsx
@@ -913,10 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123354688</v>
+        <v>123352616</v>
       </c>
       <c r="B4" t="n">
-        <v>57644</v>
+        <v>92271</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,46 +925,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Ramsebo Gölkullen, Hultsfred, Ramsebo Gölkullen, Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>539536</v>
+        <v>539470</v>
       </c>
       <c r="R4" t="n">
-        <v>6348529</v>
+        <v>6348569</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1131,10 +1126,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123353224</v>
+        <v>123353749</v>
       </c>
       <c r="B6" t="n">
-        <v>98079</v>
+        <v>92271</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1143,25 +1138,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1171,10 +1166,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>539470</v>
+        <v>539463</v>
       </c>
       <c r="R6" t="n">
-        <v>6348541</v>
+        <v>6348578</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1233,10 +1228,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123352616</v>
+        <v>123354675</v>
       </c>
       <c r="B7" t="n">
-        <v>92271</v>
+        <v>57507</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1245,41 +1240,46 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Ramsebo Gölkullen, Hultsfred, Ramsebo Gölkullen, Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>539470</v>
+        <v>539542</v>
       </c>
       <c r="R7" t="n">
-        <v>6348569</v>
+        <v>6348526</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1442,10 +1442,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123352763</v>
+        <v>123352575</v>
       </c>
       <c r="B9" t="n">
-        <v>98079</v>
+        <v>92271</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1454,25 +1454,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1482,13 +1482,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>539512</v>
+        <v>539489</v>
       </c>
       <c r="R9" t="n">
-        <v>6348548</v>
+        <v>6348577</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1544,10 +1544,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123354675</v>
+        <v>123353224</v>
       </c>
       <c r="B10" t="n">
-        <v>57507</v>
+        <v>98079</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1556,46 +1556,41 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Ramsebo Gölkullen, Hultsfred, Ramsebo Gölkullen, Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>539542</v>
+        <v>539470</v>
       </c>
       <c r="R10" t="n">
-        <v>6348526</v>
+        <v>6348541</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1651,10 +1646,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123353834</v>
+        <v>123352400</v>
       </c>
       <c r="B11" t="n">
-        <v>92271</v>
+        <v>57507</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1663,25 +1658,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1691,13 +1686,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>539458</v>
+        <v>539450</v>
       </c>
       <c r="R11" t="n">
-        <v>6348572</v>
+        <v>6348650</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1731,7 +1726,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>God förekomst, spridd i slänten</t>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1758,10 +1753,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123353749</v>
+        <v>123354802</v>
       </c>
       <c r="B12" t="n">
-        <v>92271</v>
+        <v>100257</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1774,21 +1769,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>222498</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1798,13 +1793,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>539463</v>
+        <v>539539</v>
       </c>
       <c r="R12" t="n">
-        <v>6348578</v>
+        <v>6348519</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1860,10 +1855,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123352400</v>
+        <v>123352763</v>
       </c>
       <c r="B13" t="n">
-        <v>57507</v>
+        <v>98079</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1872,25 +1867,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1900,10 +1895,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>539450</v>
+        <v>539512</v>
       </c>
       <c r="R13" t="n">
-        <v>6348650</v>
+        <v>6348548</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1936,11 +1931,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-03-21</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1967,10 +1957,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123354802</v>
+        <v>123354688</v>
       </c>
       <c r="B14" t="n">
-        <v>100257</v>
+        <v>57644</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1979,38 +1969,43 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222498</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Ramsebo Gölkullen, Hultsfred, Ramsebo Gölkullen, Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>539539</v>
+        <v>539536</v>
       </c>
       <c r="R14" t="n">
-        <v>6348519</v>
+        <v>6348529</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2069,7 +2064,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123352575</v>
+        <v>123353834</v>
       </c>
       <c r="B15" t="n">
         <v>92271</v>
@@ -2109,13 +2104,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>539489</v>
+        <v>539458</v>
       </c>
       <c r="R15" t="n">
-        <v>6348577</v>
+        <v>6348572</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2145,6 +2140,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>God förekomst, spridd i slänten</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 37626-2024 artfynd.xlsx
+++ b/artfynd/A 37626-2024 artfynd.xlsx
@@ -1335,10 +1335,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123352848</v>
+        <v>123352575</v>
       </c>
       <c r="B8" t="n">
-        <v>57644</v>
+        <v>92271</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1347,46 +1347,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Ramsebo Gölkullen, Hultsfred, Ramsebo Gölkullen, Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>539517</v>
+        <v>539489</v>
       </c>
       <c r="R8" t="n">
-        <v>6348531</v>
+        <v>6348577</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1442,10 +1437,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123352575</v>
+        <v>123352848</v>
       </c>
       <c r="B9" t="n">
-        <v>92271</v>
+        <v>57644</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1454,41 +1449,46 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Ramsebo Gölkullen, Hultsfred, Ramsebo Gölkullen, Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>539489</v>
+        <v>539517</v>
       </c>
       <c r="R9" t="n">
-        <v>6348577</v>
+        <v>6348531</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1646,10 +1646,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123352400</v>
+        <v>123354802</v>
       </c>
       <c r="B11" t="n">
-        <v>57507</v>
+        <v>100257</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1658,25 +1658,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1686,13 +1686,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>539450</v>
+        <v>539539</v>
       </c>
       <c r="R11" t="n">
-        <v>6348650</v>
+        <v>6348519</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1722,11 +1722,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-03-21</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1753,10 +1748,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123354802</v>
+        <v>123352400</v>
       </c>
       <c r="B12" t="n">
-        <v>100257</v>
+        <v>57507</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1765,25 +1760,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1793,13 +1788,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>539539</v>
+        <v>539450</v>
       </c>
       <c r="R12" t="n">
-        <v>6348519</v>
+        <v>6348650</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1829,6 +1824,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 37626-2024 artfynd.xlsx
+++ b/artfynd/A 37626-2024 artfynd.xlsx
@@ -913,10 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123352616</v>
+        <v>123354688</v>
       </c>
       <c r="B4" t="n">
-        <v>92271</v>
+        <v>57644</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,41 +925,46 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Ramsebo Gölkullen, Hultsfred, Ramsebo Gölkullen, Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>539470</v>
+        <v>539536</v>
       </c>
       <c r="R4" t="n">
-        <v>6348569</v>
+        <v>6348529</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1015,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123354501</v>
+        <v>123354802</v>
       </c>
       <c r="B5" t="n">
-        <v>105056</v>
+        <v>100257</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,45 +1032,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>340</v>
+        <v>222498</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ryl</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chimaphila umbellata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) W. P. C. Barton</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Ramsebo Gölkullen, Hultsfred, Ramsebo Gölkullen, Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>539552</v>
+        <v>539539</v>
       </c>
       <c r="R5" t="n">
-        <v>6348545</v>
+        <v>6348519</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1095,11 +1096,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-03-21</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>10 plantor, känd lokal</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1126,10 +1122,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123353749</v>
+        <v>123352763</v>
       </c>
       <c r="B6" t="n">
-        <v>92271</v>
+        <v>98079</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1138,25 +1134,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1166,13 +1162,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>539463</v>
+        <v>539512</v>
       </c>
       <c r="R6" t="n">
-        <v>6348578</v>
+        <v>6348548</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1228,10 +1224,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123354675</v>
+        <v>123354501</v>
       </c>
       <c r="B7" t="n">
-        <v>57507</v>
+        <v>105056</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1240,31 +1236,30 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>340</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ryl</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chimaphila umbellata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>(L.) W. P. C. Barton</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>10</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1273,13 +1268,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>539542</v>
+        <v>539552</v>
       </c>
       <c r="R7" t="n">
-        <v>6348526</v>
+        <v>6348545</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1309,6 +1304,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>10 plantor, känd lokal</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1335,10 +1335,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123352575</v>
+        <v>123354675</v>
       </c>
       <c r="B8" t="n">
-        <v>92271</v>
+        <v>57507</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1347,41 +1347,46 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Ramsebo Gölkullen, Hultsfred, Ramsebo Gölkullen, Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>539489</v>
+        <v>539542</v>
       </c>
       <c r="R8" t="n">
-        <v>6348577</v>
+        <v>6348526</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1437,10 +1442,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123352848</v>
+        <v>123352616</v>
       </c>
       <c r="B9" t="n">
-        <v>57644</v>
+        <v>92271</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1449,46 +1454,41 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Ramsebo Gölkullen, Hultsfred, Ramsebo Gölkullen, Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>539517</v>
+        <v>539470</v>
       </c>
       <c r="R9" t="n">
-        <v>6348531</v>
+        <v>6348569</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1544,10 +1544,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123353224</v>
+        <v>123352848</v>
       </c>
       <c r="B10" t="n">
-        <v>98079</v>
+        <v>57644</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1556,41 +1556,46 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Ramsebo Gölkullen, Hultsfred, Ramsebo Gölkullen, Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>539470</v>
+        <v>539517</v>
       </c>
       <c r="R10" t="n">
-        <v>6348541</v>
+        <v>6348531</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1646,10 +1651,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123354802</v>
+        <v>123352575</v>
       </c>
       <c r="B11" t="n">
-        <v>100257</v>
+        <v>92271</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1662,21 +1667,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222498</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1686,13 +1691,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>539539</v>
+        <v>539489</v>
       </c>
       <c r="R11" t="n">
-        <v>6348519</v>
+        <v>6348577</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1748,10 +1753,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123352400</v>
+        <v>123353749</v>
       </c>
       <c r="B12" t="n">
-        <v>57507</v>
+        <v>92271</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1760,25 +1765,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1788,13 +1793,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>539450</v>
+        <v>539463</v>
       </c>
       <c r="R12" t="n">
-        <v>6348650</v>
+        <v>6348578</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1824,11 +1829,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-03-21</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1855,7 +1855,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123352763</v>
+        <v>123353224</v>
       </c>
       <c r="B13" t="n">
         <v>98079</v>
@@ -1895,13 +1895,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>539512</v>
+        <v>539470</v>
       </c>
       <c r="R13" t="n">
-        <v>6348548</v>
+        <v>6348541</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1957,10 +1957,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123354688</v>
+        <v>123353834</v>
       </c>
       <c r="B14" t="n">
-        <v>57644</v>
+        <v>92271</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1969,43 +1969,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Ramsebo Gölkullen, Hultsfred, Ramsebo Gölkullen, Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>539536</v>
+        <v>539458</v>
       </c>
       <c r="R14" t="n">
-        <v>6348529</v>
+        <v>6348572</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2038,6 +2033,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>God förekomst, spridd i slänten</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2064,10 +2064,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123353834</v>
+        <v>123352400</v>
       </c>
       <c r="B15" t="n">
-        <v>92271</v>
+        <v>57507</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2076,25 +2076,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2104,13 +2104,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>539458</v>
+        <v>539450</v>
       </c>
       <c r="R15" t="n">
-        <v>6348572</v>
+        <v>6348650</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>God förekomst, spridd i slänten</t>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 37626-2024 artfynd.xlsx
+++ b/artfynd/A 37626-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,57 +675,51 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>99069829</v>
+        <v>99069692</v>
       </c>
       <c r="B2" t="n">
-        <v>56540</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106205</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>340</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ryl</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chimaphila umbellata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) W. P. C. Barton</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Ramsebo Gölkullen, Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>539549.2649325953</v>
+        <v>539563</v>
       </c>
       <c r="R2" t="n">
-        <v>6348537.329554083</v>
+        <v>6348562</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -755,24 +749,9 @@
           <t>2022-03-12</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-03-12</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Sångläte</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,55 +778,52 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>99069809</v>
+        <v>123354501</v>
       </c>
       <c r="B3" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106205</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>340</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ryl</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Chimaphila umbellata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
+          <t>(L.) W. P. C. Barton</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Ramsebo Gölkullen, Hultsfred, Sm</t>
+          <t>Ramsebo Gölkullen, Hultsfred, Ramsebo Gölkullen, Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>539549.2649325953</v>
+        <v>539552</v>
       </c>
       <c r="R3" t="n">
-        <v>6348537.329554083</v>
+        <v>6348545</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -871,22 +847,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-03-12</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-03-12</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>10 plantor, känd lokal</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -913,37 +884,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123353224</v>
+        <v>123352575</v>
       </c>
       <c r="B4" t="n">
-        <v>98079</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -953,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>539470</v>
+        <v>539489</v>
       </c>
       <c r="R4" t="n">
-        <v>6348541</v>
+        <v>6348577</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -1015,37 +981,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123352763</v>
+        <v>123352616</v>
       </c>
       <c r="B5" t="n">
-        <v>98079</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1055,13 +1016,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>539512</v>
+        <v>539470</v>
       </c>
       <c r="R5" t="n">
-        <v>6348548</v>
+        <v>6348569</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1117,19 +1078,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123352575</v>
+        <v>123353749</v>
       </c>
       <c r="B6" t="n">
-        <v>92271</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1157,10 +1113,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>539489</v>
+        <v>539463</v>
       </c>
       <c r="R6" t="n">
-        <v>6348577</v>
+        <v>6348578</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1219,15 +1175,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123352400</v>
+        <v>123353834</v>
       </c>
       <c r="B7" t="n">
-        <v>57507</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1235,21 +1186,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1259,13 +1210,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>539450</v>
+        <v>539458</v>
       </c>
       <c r="R7" t="n">
-        <v>6348650</v>
+        <v>6348572</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1299,7 +1250,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Födosökshack</t>
+          <t>God förekomst, spridd i slänten</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1326,58 +1277,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123354688</v>
+        <v>123352400</v>
       </c>
       <c r="B8" t="n">
-        <v>57644</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Ramsebo Gölkullen, Hultsfred, Ramsebo Gölkullen, Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>539536</v>
+        <v>539450</v>
       </c>
       <c r="R8" t="n">
-        <v>6348529</v>
+        <v>6348650</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1407,6 +1348,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1433,43 +1379,38 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123352848</v>
+        <v>123354675</v>
       </c>
       <c r="B9" t="n">
-        <v>57644</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1478,10 +1419,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>539517</v>
+        <v>539542</v>
       </c>
       <c r="R9" t="n">
-        <v>6348531</v>
+        <v>6348526</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1540,53 +1481,55 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123353749</v>
+        <v>99069829</v>
       </c>
       <c r="B10" t="n">
-        <v>92271</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Ramsebo Gölkullen, Hultsfred, Ramsebo Gölkullen, Hultsfred, Sm</t>
+          <t>Ramsebo Gölkullen, Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>539463</v>
+        <v>539549</v>
       </c>
       <c r="R10" t="n">
-        <v>6348578</v>
+        <v>6348537</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1610,12 +1553,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-03-21</t>
+          <t>2022-03-12</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-03-21</t>
+          <t>2022-03-12</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Sångläte</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1642,50 +1590,50 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123354802</v>
+        <v>123352848</v>
       </c>
       <c r="B11" t="n">
-        <v>100257</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222498</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Ramsebo Gölkullen, Hultsfred, Ramsebo Gölkullen, Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>539539</v>
+        <v>539517</v>
       </c>
       <c r="R11" t="n">
-        <v>6348519</v>
+        <v>6348531</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1744,50 +1692,50 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123353834</v>
+        <v>123354688</v>
       </c>
       <c r="B12" t="n">
-        <v>92271</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Ramsebo Gölkullen, Hultsfred, Ramsebo Gölkullen, Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>539458</v>
+        <v>539536</v>
       </c>
       <c r="R12" t="n">
-        <v>6348572</v>
+        <v>6348529</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1820,11 +1768,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-03-21</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>God förekomst, spridd i slänten</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1851,15 +1794,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123354675</v>
+        <v>134052080</v>
       </c>
       <c r="B13" t="n">
-        <v>57507</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>110159</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1867,42 +1805,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>220299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Ramsebo Gölkullen, Hultsfred, Ramsebo Gölkullen, Hultsfred, Sm</t>
+          <t>Hultsfred, Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>539542</v>
+        <v>539269</v>
       </c>
       <c r="R13" t="n">
-        <v>6348526</v>
+        <v>6348829</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1926,12 +1859,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-03-21</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-03-21</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1958,54 +1891,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123354501</v>
+        <v>134052153</v>
       </c>
       <c r="B14" t="n">
-        <v>105056</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>110159</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>340</v>
+        <v>220299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ryl</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chimaphila umbellata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) W. P. C. Barton</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Ramsebo Gölkullen, Hultsfred, Ramsebo Gölkullen, Hultsfred, Sm</t>
+          <t>Hultsfred, Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>539552</v>
+        <v>539367</v>
       </c>
       <c r="R14" t="n">
-        <v>6348545</v>
+        <v>6348783</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2032,17 +1956,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-03-21</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-03-21</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>10 plantor, känd lokal</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2069,37 +1988,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123352616</v>
+        <v>134052261</v>
       </c>
       <c r="B15" t="n">
-        <v>92271</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>110159</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>220299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2109,13 +2023,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>539470</v>
+        <v>539508</v>
       </c>
       <c r="R15" t="n">
-        <v>6348569</v>
+        <v>6348709</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2139,12 +2053,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-03-21</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-03-21</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2168,6 +2082,598 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>99070008</v>
+      </c>
+      <c r="B16" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Ramsebo Gölkullen, Hultsfred, Sm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>539552</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6348564</v>
+      </c>
+      <c r="S16" t="n">
+        <v>25</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Hultsfred</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Virserum</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2022-03-12</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2022-03-12</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>123352763</v>
+      </c>
+      <c r="B17" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Ramsebo Gölkullen, Hultsfred, Ramsebo Gölkullen, Hultsfred, Sm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>539512</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6348548</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Hultsfred</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Virserum</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>123353224</v>
+      </c>
+      <c r="B18" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Ramsebo Gölkullen, Hultsfred, Ramsebo Gölkullen, Hultsfred, Sm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>539470</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6348541</v>
+      </c>
+      <c r="S18" t="n">
+        <v>15</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Hultsfred</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Virserum</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>99069700</v>
+      </c>
+      <c r="B19" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Ramsebo Gölkullen, Hultsfred, Sm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>539563</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6348562</v>
+      </c>
+      <c r="S19" t="n">
+        <v>25</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Hultsfred</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Virserum</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2022-03-12</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2022-03-12</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>99069809</v>
+      </c>
+      <c r="B20" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Ramsebo Gölkullen, Hultsfred, Sm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>539549</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6348537</v>
+      </c>
+      <c r="S20" t="n">
+        <v>25</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Hultsfred</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Virserum</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2022-03-12</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2022-03-12</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>123354802</v>
+      </c>
+      <c r="B21" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Ramsebo Gölkullen, Hultsfred, Ramsebo Gölkullen, Hultsfred, Sm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>539539</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6348519</v>
+      </c>
+      <c r="S21" t="n">
+        <v>25</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Hultsfred</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Virserum</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 37626-2024 artfynd.xlsx
+++ b/artfynd/A 37626-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AZ21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -775,6 +780,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99069692</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -881,6 +891,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123354501</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123352575</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1075,6 +1095,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123352616</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1172,6 +1197,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123353749</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1274,6 +1304,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123353834</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1376,6 +1411,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123352400</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1478,6 +1518,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123354675</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1587,6 +1632,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99069829</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1689,6 +1739,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123352848</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1791,6 +1846,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123354688</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1888,6 +1948,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134052080</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1985,6 +2050,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134052153</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2082,6 +2152,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134052261</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2185,6 +2260,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99070008</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2282,6 +2362,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123352763</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2379,6 +2464,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123353224</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2478,6 +2568,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99069700</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2577,6 +2672,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99069809</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2674,8 +2774,35 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123354802</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>